--- a/output/yearly_surface_area_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_89_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497628458963</v>
+        <v>10.8449762790035</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907177595978</v>
+        <v>37.78907175649503</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.759512870188536</v>
+        <v>5.439864029231576</v>
       </c>
       <c r="C2" t="n">
-        <v>9.226464924511523</v>
+        <v>8.983973241562561</v>
       </c>
       <c r="D2" t="n">
-        <v>25.21913502669207</v>
+        <v>31.80273513137118</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.00953973960199</v>
+        <v>17.22967220953152</v>
       </c>
       <c r="C3" t="n">
-        <v>32.9965403397353</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D3" t="n">
-        <v>57.95747572021045</v>
+        <v>68.1283819362074</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.34524070119216</v>
+        <v>32.02166486941822</v>
       </c>
       <c r="C4" t="n">
-        <v>65.14092367218436</v>
+        <v>60.76331065894783</v>
       </c>
       <c r="D4" t="n">
-        <v>80.02225537315752</v>
+        <v>105.5987465641954</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.79790850830796</v>
+        <v>39.24536447726625</v>
       </c>
       <c r="C5" t="n">
-        <v>137.9846398318892</v>
+        <v>110.7656847316464</v>
       </c>
       <c r="D5" t="n">
-        <v>59.37119241432587</v>
+        <v>85.58385611771571</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.84913931537804</v>
+        <v>36.70951015719674</v>
       </c>
       <c r="C6" t="n">
-        <v>186.2846633854238</v>
+        <v>133.0317226639641</v>
       </c>
       <c r="D6" t="n">
-        <v>43.43153668817465</v>
+        <v>54.42023874180921</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.76931465169778</v>
+        <v>25.33203601268044</v>
       </c>
       <c r="C7" t="n">
-        <v>168.8203534745772</v>
+        <v>119.3540136483975</v>
       </c>
       <c r="D7" t="n">
-        <v>38.32743037379547</v>
+        <v>41.68108053150257</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>104.3106935762236</v>
+        <v>79.94371555681776</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>48.92343334573128</v>
+        <v>45.48437113775471</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -926,7 +926,7 @@
         <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -962,7 +962,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
         <v>21.14193681095506</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.646554511388065</v>
+        <v>7.663455447751835</v>
       </c>
       <c r="C21" t="n">
-        <v>92.71447345058029</v>
+        <v>92.91939730399099</v>
       </c>
       <c r="D21" t="n">
-        <v>7.646554511388065</v>
+        <v>7.663455447751835</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.802128932098649</v>
+        <v>6.412776004140166</v>
       </c>
       <c r="C2" t="n">
-        <v>11.70734137314321</v>
+        <v>16.09182662030947</v>
       </c>
       <c r="D2" t="n">
-        <v>20.37813709705104</v>
+        <v>34.95218176659494</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.89311267342411</v>
+        <v>17.57819264453914</v>
       </c>
       <c r="C3" t="n">
-        <v>34.13045893814036</v>
+        <v>32.80019079888594</v>
       </c>
       <c r="D3" t="n">
-        <v>62.87603171848697</v>
+        <v>75.90873249236338</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.65230674844316</v>
+        <v>32.28968199267759</v>
       </c>
       <c r="C4" t="n">
-        <v>72.46672504127406</v>
+        <v>68.86763795750525</v>
       </c>
       <c r="D4" t="n">
-        <v>87.66712474612743</v>
+        <v>114.0604300270987</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.83503499462009</v>
+        <v>42.92691836819179</v>
       </c>
       <c r="C5" t="n">
-        <v>128.1671627894211</v>
+        <v>110.127548723886</v>
       </c>
       <c r="D5" t="n">
-        <v>72.0602814917159</v>
+        <v>100.187353218387</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.97368240509714</v>
+        <v>43.9548082145382</v>
       </c>
       <c r="C6" t="n">
-        <v>201.7815508969597</v>
+        <v>153.1978022568978</v>
       </c>
       <c r="D6" t="n">
-        <v>50.19381487502668</v>
+        <v>66.85800040691205</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.99185258539232</v>
+        <v>33.59638818703009</v>
       </c>
       <c r="C7" t="n">
-        <v>212.7172385745649</v>
+        <v>151.9922160760827</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80085375142069</v>
+        <v>46.59178254814513</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.27799883121787</v>
+        <v>19.86075605691297</v>
       </c>
       <c r="C8" t="n">
-        <v>158.135011461555</v>
+        <v>115.4927999275948</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>83.53593040665682</v>
+        <v>70.44530651822986</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>43.2754388031994</v>
+        <v>41.42484438069417</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1273,7 +1273,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
         <v>22.93362637120549</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.8157655244698</v>
+        <v>7.839124850378125</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6279811275487</v>
+        <v>100.9287324486184</v>
       </c>
       <c r="D21" t="n">
-        <v>8.792736215028524</v>
+        <v>8.819015456675391</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.009277697694727</v>
+        <v>6.825110039923826</v>
       </c>
       <c r="C2" t="n">
-        <v>13.9447443911217</v>
+        <v>17.3298104753647</v>
       </c>
       <c r="D2" t="n">
-        <v>29.50937249425062</v>
+        <v>31.33247798103695</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.47372647726148</v>
+        <v>18.92318699935727</v>
       </c>
       <c r="C3" t="n">
-        <v>38.80848674887642</v>
+        <v>45.95070129727196</v>
       </c>
       <c r="D3" t="n">
-        <v>63.52889394181111</v>
+        <v>82.90859362364314</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.73339089726815</v>
+        <v>32.00890214926301</v>
       </c>
       <c r="C4" t="n">
-        <v>76.97196525606267</v>
+        <v>73.70470889632929</v>
       </c>
       <c r="D4" t="n">
-        <v>95.91184196639215</v>
+        <v>121.48833315743</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.14781160164732</v>
+        <v>44.8167826988669</v>
       </c>
       <c r="C5" t="n">
-        <v>130.0079397348839</v>
+        <v>115.9689475641545</v>
       </c>
       <c r="D5" t="n">
-        <v>82.14773915285187</v>
+        <v>114.2999764669349</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.08564270111029</v>
+        <v>49.95230493978197</v>
       </c>
       <c r="C6" t="n">
-        <v>201.3387826823444</v>
+        <v>162.8984513225605</v>
       </c>
       <c r="D6" t="n">
-        <v>58.64666260859173</v>
+        <v>78.41022564278425</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.59745205019235</v>
+        <v>41.02232782195297</v>
       </c>
       <c r="C7" t="n">
-        <v>243.9780489731918</v>
+        <v>180.1988093667978</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>53.35896947351839</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.45457454926205</v>
+        <v>26.45319189093031</v>
       </c>
       <c r="C8" t="n">
-        <v>207.9537987135594</v>
+        <v>151.0418842983718</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.08906130364597</v>
+        <v>13.86718632248619</v>
       </c>
       <c r="C9" t="n">
-        <v>129.3531140161512</v>
+        <v>101.2859288994392</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>64.62845137056753</v>
+        <v>58.2225476003571</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09319358310798</v>
+        <v>38.73780091417063</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.969115065702066</v>
+        <v>7.998296834743764</v>
       </c>
       <c r="C21" t="n">
-        <v>107.5830533869779</v>
+        <v>108.9767943733838</v>
       </c>
       <c r="D21" t="n">
-        <v>9.961393832127584</v>
+        <v>9.997871043429704</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.599888905023806</v>
+        <v>6.33718143091316</v>
       </c>
       <c r="C2" t="n">
-        <v>9.816495294763856</v>
+        <v>11.92234412037327</v>
       </c>
       <c r="D2" t="n">
-        <v>24.21677062065607</v>
+        <v>25.86119802526948</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.19316761802514</v>
+        <v>22.25622045527519</v>
       </c>
       <c r="C3" t="n">
-        <v>56.73519982842318</v>
+        <v>65.78691366157877</v>
       </c>
       <c r="D3" t="n">
-        <v>69.2672092731337</v>
+        <v>89.96245087865647</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.72665753205866</v>
+        <v>21.5307089018368</v>
       </c>
       <c r="C4" t="n">
-        <v>105.5349329634194</v>
+        <v>97.50718198579321</v>
       </c>
       <c r="D4" t="n">
-        <v>92.54248384541708</v>
+        <v>120.3779765039269</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.32971266437347</v>
+        <v>28.12707172667112</v>
       </c>
       <c r="C5" t="n">
-        <v>120.2886374628405</v>
+        <v>97.34028487607128</v>
       </c>
       <c r="D5" t="n">
-        <v>56.32777453116076</v>
+        <v>77.55806863549803</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.04911274740813</v>
+        <v>25.43904651244335</v>
       </c>
       <c r="C6" t="n">
-        <v>160.684610249484</v>
+        <v>118.6618815169035</v>
       </c>
       <c r="D6" t="n">
-        <v>29.66547037922588</v>
+        <v>35.13969557810609</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.1456428175938</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>146.2431015200134</v>
+        <v>106.1789594574053</v>
       </c>
       <c r="D7" t="n">
-        <v>27.84727363096077</v>
+        <v>29.22466566001905</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>95.29824965123788</v>
+        <v>74.60300804571511</v>
       </c>
       <c r="D8" t="n">
-        <v>26.62008900065226</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>49.25624581747095</v>
+        <v>44.37499623195582</v>
       </c>
       <c r="D9" t="n">
-        <v>26.95781021091316</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
         <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.402737542919445</v>
+        <v>3.867104207028186</v>
       </c>
       <c r="C2" t="n">
-        <v>4.770312094935251</v>
+        <v>5.514476854754333</v>
       </c>
       <c r="D2" t="n">
-        <v>17.41620427333842</v>
+        <v>18.05826727191583</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.68895020866978</v>
+        <v>22.59001467471911</v>
       </c>
       <c r="C3" t="n">
-        <v>48.65050748395069</v>
+        <v>57.31443097392879</v>
       </c>
       <c r="D3" t="n">
-        <v>72.01610284502478</v>
+        <v>90.99328596811563</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.61852641587127</v>
+        <v>30.2093586073786</v>
       </c>
       <c r="C4" t="n">
-        <v>124.9087421590259</v>
+        <v>131.4560175986479</v>
       </c>
       <c r="D4" t="n">
-        <v>104.105508306036</v>
+        <v>134.2127651521729</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.63681976935347</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="C5" t="n">
-        <v>156.0733412826367</v>
+        <v>136.3402124272758</v>
       </c>
       <c r="D5" t="n">
-        <v>69.70408700152355</v>
+        <v>96.62851779049234</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.75855648468008</v>
+        <v>29.90698031447059</v>
       </c>
       <c r="C6" t="n">
-        <v>180.8909414982919</v>
+        <v>139.6732458831937</v>
       </c>
       <c r="D6" t="n">
-        <v>35.58246379272141</v>
+        <v>43.67304662341937</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>182.7140469850781</v>
+        <v>132.3494080095125</v>
       </c>
       <c r="D7" t="n">
-        <v>30.18285141936394</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>124.6721409623024</v>
+        <v>97.38446352276235</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>53.36093296892687</v>
+        <v>48.59062087399162</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
         <v>29.31989518733098</v>
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.972732048459342</v>
+        <v>3.614795047036756</v>
       </c>
       <c r="C2" t="n">
-        <v>10.46248528415826</v>
+        <v>6.060328578315561</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1114615743944</v>
+        <v>17.8373740384603</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.64414966717292</v>
+        <v>17.88744317137688</v>
       </c>
       <c r="C3" t="n">
-        <v>33.35978699030662</v>
+        <v>38.53850613020854</v>
       </c>
       <c r="D3" t="n">
-        <v>69.22303062644259</v>
+        <v>84.77882300023332</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.26415655236718</v>
+        <v>35.96534539737765</v>
       </c>
       <c r="C4" t="n">
-        <v>123.0453850163655</v>
+        <v>137.1481907878709</v>
       </c>
       <c r="D4" t="n">
-        <v>114.507125232531</v>
+        <v>146.8350953856742</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.03014074585795</v>
+        <v>37.60093707265284</v>
       </c>
       <c r="C5" t="n">
-        <v>190.7781226277615</v>
+        <v>188.4710155227814</v>
       </c>
       <c r="D5" t="n">
-        <v>87.62098260402784</v>
+        <v>118.4724042099839</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.50825187782615</v>
+        <v>35.66296710446964</v>
       </c>
       <c r="C6" t="n">
-        <v>213.3740277887061</v>
+        <v>174.6116831819292</v>
       </c>
       <c r="D6" t="n">
-        <v>46.41015922285948</v>
+        <v>59.61270234957058</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.852943133008</v>
+        <v>23.59532432386784</v>
       </c>
       <c r="C7" t="n">
-        <v>219.9635183796106</v>
+        <v>165.346930096952</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>174.2405825497239</v>
+        <v>132.3494080095125</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2069942013426</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>95.07342942696533</v>
+        <v>78.32186834940201</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>44.4142661401257</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
         <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.807397523518378</v>
+        <v>2.189297380470387</v>
       </c>
       <c r="C2" t="n">
-        <v>5.05992766768806</v>
+        <v>2.926589906359742</v>
       </c>
       <c r="D2" t="n">
-        <v>11.29402558965531</v>
+        <v>12.45052438525805</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.93729132011522</v>
+        <v>17.3131207643925</v>
       </c>
       <c r="C3" t="n">
-        <v>38.51396243760237</v>
+        <v>34.48388811166921</v>
       </c>
       <c r="D3" t="n">
-        <v>68.84996649882882</v>
+        <v>83.3356538749905</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.4548365911693</v>
+        <v>39.36022895866312</v>
       </c>
       <c r="C4" t="n">
-        <v>121.1437397132394</v>
+        <v>137.0716144669396</v>
       </c>
       <c r="D4" t="n">
-        <v>123.0453850163655</v>
+        <v>156.368847341615</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.89546138392689</v>
+        <v>38.53359739168732</v>
       </c>
       <c r="C5" t="n">
-        <v>233.2632545290422</v>
+        <v>231.6188271244288</v>
       </c>
       <c r="D5" t="n">
-        <v>92.08793465835082</v>
+        <v>124.6328710541326</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.58496706747763</v>
+        <v>28.82018560586937</v>
       </c>
       <c r="C6" t="n">
-        <v>250.6470611281405</v>
+        <v>208.0205575574482</v>
       </c>
       <c r="D6" t="n">
-        <v>45.44411948188061</v>
+        <v>57.92213280285758</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.665486074759095</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>229.2459429232642</v>
+        <v>172.0542304123663</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>119.5817791157827</v>
+        <v>96.63342652901355</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.962513660789374</v>
+        <v>2.176534660315179</v>
       </c>
       <c r="C2" t="n">
-        <v>6.800566347317655</v>
+        <v>7.767587836000764</v>
       </c>
       <c r="D2" t="n">
-        <v>10.23177457366026</v>
+        <v>16.62786086682823</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.70595871481147</v>
+        <v>12.64491043069892</v>
       </c>
       <c r="C3" t="n">
-        <v>29.31007771028852</v>
+        <v>23.16433708170349</v>
       </c>
       <c r="D3" t="n">
-        <v>62.74840451693489</v>
+        <v>75.16751297565703</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.50664823531614</v>
+        <v>36.70558316637975</v>
       </c>
       <c r="C4" t="n">
-        <v>109.1340200471882</v>
+        <v>112.8224461720434</v>
       </c>
       <c r="D4" t="n">
-        <v>127.8952186753447</v>
+        <v>160.8740875564036</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.25227776892498</v>
+        <v>46.82936549257286</v>
       </c>
       <c r="C5" t="n">
-        <v>230.5143609571511</v>
+        <v>242.8352946454486</v>
       </c>
       <c r="D5" t="n">
-        <v>110.0784613386736</v>
+        <v>146.1822331623501</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.71580155404972</v>
+        <v>37.19253002768617</v>
       </c>
       <c r="C6" t="n">
-        <v>304.0610084730967</v>
+        <v>277.494915596178</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4516957260741</v>
+        <v>77.40393424593128</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.81006502919063</v>
+        <v>15.9897248590678</v>
       </c>
       <c r="C7" t="n">
-        <v>288.5336867827291</v>
+        <v>227.8685508942059</v>
       </c>
       <c r="D7" t="n">
-        <v>36.89015173477814</v>
+        <v>41.26187426178919</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>190.3461536378928</v>
+        <v>147.5370449942107</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>72.77499382040753</v>
+        <v>62.79061966821748</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.341067364001143</v>
+        <v>1.524654184695297</v>
       </c>
       <c r="C2" t="n">
-        <v>5.378995671568275</v>
+        <v>4.217588137444298</v>
       </c>
       <c r="D2" t="n">
-        <v>7.819620464325845</v>
+        <v>12.39652826152447</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.154797342101507</v>
+        <v>10.62741889847172</v>
       </c>
       <c r="C3" t="n">
-        <v>28.57867567062465</v>
+        <v>26.69862881699201</v>
       </c>
       <c r="D3" t="n">
-        <v>58.13419030697487</v>
+        <v>72.08973392284329</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.51191682673587</v>
+        <v>32.54493639578177</v>
       </c>
       <c r="C4" t="n">
-        <v>97.3540293439307</v>
+        <v>92.44038208417543</v>
       </c>
       <c r="D4" t="n">
-        <v>129.6309486164531</v>
+        <v>161.8312915680442</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.56567627075797</v>
+        <v>51.12451169865266</v>
       </c>
       <c r="C5" t="n">
-        <v>225.4092728950677</v>
+        <v>238.1474493576701</v>
       </c>
       <c r="D5" t="n">
-        <v>123.1847931903686</v>
+        <v>161.7674779672682</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.19002675292993</v>
+        <v>43.14977509705582</v>
       </c>
       <c r="C6" t="n">
-        <v>338.3151676219721</v>
+        <v>324.0660814425339</v>
       </c>
       <c r="D6" t="n">
-        <v>69.19259644761097</v>
+        <v>90.44547074914593</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.07335334037803</v>
+        <v>14.19312656029614</v>
       </c>
       <c r="C7" t="n">
-        <v>345.1265331940364</v>
+        <v>285.0602634051039</v>
       </c>
       <c r="D7" t="n">
-        <v>40.78278138211675</v>
+        <v>46.35223610830891</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>239.2470067864264</v>
+        <v>186.5075201142878</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>80.09686819868024</v>
+        <v>68.89218165011141</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3386,7 +3386,7 @@
         <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
         <v>19.7439280801076</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.379756435094268</v>
+        <v>3.265292864324891</v>
       </c>
       <c r="C2" t="n">
-        <v>20.39679030343173</v>
+        <v>4.722206457427157</v>
       </c>
       <c r="D2" t="n">
-        <v>7.522150909939061</v>
+        <v>18.23989059720149</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.024404823885928</v>
+        <v>8.109236037078654</v>
       </c>
       <c r="C3" t="n">
-        <v>24.94620916491145</v>
+        <v>21.94696992843745</v>
       </c>
       <c r="D3" t="n">
-        <v>52.3713312830461</v>
+        <v>66.4545021004666</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.40682876465245</v>
+        <v>26.85276320655876</v>
       </c>
       <c r="C4" t="n">
-        <v>86.03349656626072</v>
+        <v>81.22195106774711</v>
       </c>
       <c r="D4" t="n">
-        <v>128.5716428435708</v>
+        <v>160.35081603004</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.14214209960009</v>
+        <v>50.58455046131692</v>
       </c>
       <c r="C5" t="n">
-        <v>206.0442994287994</v>
+        <v>209.9958339383928</v>
       </c>
       <c r="D5" t="n">
-        <v>133.9840179370835</v>
+        <v>173.9411494999287</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.03280825153021</v>
+        <v>51.56237117474674</v>
       </c>
       <c r="C6" t="n">
-        <v>347.0095252907819</v>
+        <v>345.7214723028101</v>
       </c>
       <c r="D6" t="n">
-        <v>84.85049058264335</v>
+        <v>111.0945702125691</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.99078872223005</v>
+        <v>25.930902112271</v>
       </c>
       <c r="C7" t="n">
-        <v>400.7611938459989</v>
+        <v>354.4688443476491</v>
       </c>
       <c r="D7" t="n">
-        <v>47.66974152740813</v>
+        <v>56.23352675155305</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.176575718044183</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="C8" t="n">
-        <v>321.9445246536565</v>
+        <v>258.4401744044516</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>152.3171745661883</v>
+        <v>123.2515520342573</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>52.10135066437823</v>
+        <v>47.68839473378882</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.499750639190632</v>
+        <v>4.522911673465055</v>
       </c>
       <c r="C2" t="n">
-        <v>10.56360529769568</v>
+        <v>9.337402415091415</v>
       </c>
       <c r="D2" t="n">
-        <v>8.462665210607506</v>
+        <v>21.04474378823463</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.737693436516854</v>
+        <v>2.384665173615502</v>
       </c>
       <c r="C2" t="n">
-        <v>12.07451501453152</v>
+        <v>2.795035713990669</v>
       </c>
       <c r="D2" t="n">
-        <v>5.595961914206819</v>
+        <v>13.56971676809941</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.905834335850317</v>
+        <v>11.51590057081509</v>
       </c>
       <c r="C3" t="n">
-        <v>43.56014563743098</v>
+        <v>24.5927799913826</v>
       </c>
       <c r="D3" t="n">
-        <v>56.17560363700249</v>
+        <v>73.63598655703201</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.91054745238907</v>
+        <v>38.00738062221102</v>
       </c>
       <c r="C4" t="n">
-        <v>122.7390797326405</v>
+        <v>118.2593649581623</v>
       </c>
       <c r="D4" t="n">
-        <v>130.2690846242135</v>
+        <v>163.3245298262036</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.59340188618836</v>
+        <v>29.50151851261666</v>
       </c>
       <c r="C5" t="n">
-        <v>298.5985642466674</v>
+        <v>300.4393411921302</v>
       </c>
       <c r="D5" t="n">
-        <v>122.3257639491526</v>
+        <v>159.0922154731956</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.14091400552181</v>
+        <v>16.1006623496477</v>
       </c>
       <c r="C6" t="n">
-        <v>325.1528761511352</v>
+        <v>294.4408627191822</v>
       </c>
       <c r="D6" t="n">
-        <v>68.34731167425446</v>
+        <v>85.93728529124456</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.73104218676538</v>
+        <v>4.850815406683489</v>
       </c>
       <c r="C7" t="n">
-        <v>226.3713856452295</v>
+        <v>181.7558612257332</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>112.2383062880166</v>
+        <v>90.79202768874502</v>
       </c>
       <c r="D8" t="n">
-        <v>23.94973524510094</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>39.71562162760046</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
         <v>18.93300447639974</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.0179745583127</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.607162049581034</v>
+        <v>6.54040320569225</v>
       </c>
       <c r="C2" t="n">
-        <v>10.02658930347267</v>
+        <v>5.225843029705771</v>
       </c>
       <c r="D2" t="n">
-        <v>13.15443748920301</v>
+        <v>23.55998140651495</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.68279768053704</v>
+        <v>9.611310024576275</v>
       </c>
       <c r="C3" t="n">
-        <v>26.62008900065226</v>
+        <v>23.52758373227481</v>
       </c>
       <c r="D3" t="n">
-        <v>10.24453729381547</v>
+        <v>20.81305133003238</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4585,7 +4585,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="D7" t="n">
         <v>32.21899615797182</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39779152280897</v>
+        <v>13.39601475374789</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1413791488234</v>
+        <v>70.13207724020955</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57621076738929</v>
+        <v>1.576001735735046</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.534692645916017</v>
+        <v>4.508185457901353</v>
       </c>
       <c r="C2" t="n">
-        <v>13.17799943410494</v>
+        <v>6.467753875577987</v>
       </c>
       <c r="D2" t="n">
-        <v>16.75646981608456</v>
+        <v>20.91122610045706</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.35377333089412</v>
+        <v>17.35239067256238</v>
       </c>
       <c r="C3" t="n">
-        <v>34.42989198793564</v>
+        <v>21.55917958525995</v>
       </c>
       <c r="D3" t="n">
-        <v>18.81519475189012</v>
+        <v>35.57362806338318</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.63058512576272</v>
+        <v>11.29500733735955</v>
       </c>
       <c r="C4" t="n">
-        <v>41.10872161992669</v>
+        <v>36.39927788265474</v>
       </c>
       <c r="D4" t="n">
-        <v>20.43311496848886</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.58368222013712</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
         <v>36.63391558396972</v>
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43910273763022</v>
+        <v>15.43514992269241</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13394158888437</v>
+        <v>86.11188904238924</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250337418448467</v>
+        <v>3.249505246882612</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.289656630481814</v>
+        <v>4.383503499462008</v>
       </c>
       <c r="C2" t="n">
-        <v>8.146542449840032</v>
+        <v>7.768569583705011</v>
       </c>
       <c r="D2" t="n">
-        <v>22.0068565383965</v>
+        <v>32.73048671188441</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.86151682043897</v>
+        <v>16.3755517068368</v>
       </c>
       <c r="C3" t="n">
-        <v>44.45353604829558</v>
+        <v>23.69448084199677</v>
       </c>
       <c r="D3" t="n">
-        <v>27.85218236948201</v>
+        <v>44.04611075103315</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.07423727709104</v>
+        <v>23.930100291016</v>
       </c>
       <c r="C4" t="n">
-        <v>66.81284001251667</v>
+        <v>46.22657240216531</v>
       </c>
       <c r="D4" t="n">
-        <v>25.2701859073129</v>
+        <v>37.94356702143497</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.02640937702343</v>
+        <v>10.21017612416683</v>
       </c>
       <c r="C5" t="n">
-        <v>45.57763716965817</v>
+        <v>40.66889864842413</v>
       </c>
       <c r="D5" t="n">
-        <v>30.01693605734623</v>
+        <v>31.95588777323368</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.39751000922872</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.2069942013426</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72752648121501</v>
+        <v>16.72369910844792</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0379115354116</v>
+        <v>102.0145645615323</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181881620303753</v>
+        <v>4.180924777111979</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.648976290236146</v>
+        <v>4.820381227851839</v>
       </c>
       <c r="C2" t="n">
-        <v>8.441066761114076</v>
+        <v>8.746390297134834</v>
       </c>
       <c r="D2" t="n">
-        <v>28.48148264790422</v>
+        <v>28.27237038689964</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.48983535115693</v>
+        <v>15.59506228196058</v>
       </c>
       <c r="C3" t="n">
-        <v>37.12478943609314</v>
+        <v>27.32203860918873</v>
       </c>
       <c r="D3" t="n">
-        <v>38.38142649752905</v>
+        <v>59.12084674974292</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.62227348023901</v>
+        <v>27.89930625928586</v>
       </c>
       <c r="C4" t="n">
-        <v>91.16411006865457</v>
+        <v>52.93976320380501</v>
       </c>
       <c r="D4" t="n">
-        <v>33.09373336245573</v>
+        <v>50.75733805726435</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.10819753611218</v>
+        <v>22.99743997198154</v>
       </c>
       <c r="C5" t="n">
-        <v>86.36925428111316</v>
+        <v>64.81989217289566</v>
       </c>
       <c r="D5" t="n">
-        <v>32.00497515844602</v>
+        <v>37.74819922828986</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.02895370950867</v>
+        <v>9.821404033285093</v>
       </c>
       <c r="C6" t="n">
-        <v>43.27053006467818</v>
+        <v>39.36611944488861</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>38.76234460677682</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.37951975538279</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
         <v>39.88448223273092</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
         <v>39.30426933952106</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>48.54251523648354</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>41.74489413227862</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04230607544442</v>
+        <v>18.04067164330244</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7045682064707</v>
+        <v>117.6939054824968</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01410202514814</v>
+        <v>6.013557214434145</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.528221322613789</v>
+        <v>5.887540982368122</v>
       </c>
       <c r="C2" t="n">
-        <v>6.938992773616455</v>
+        <v>6.12512392679585</v>
       </c>
       <c r="D2" t="n">
-        <v>22.55467175736622</v>
+        <v>23.80443658487241</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.40009539944297</v>
+        <v>14.25497666566369</v>
       </c>
       <c r="C3" t="n">
-        <v>32.5056664876119</v>
+        <v>29.13827186204533</v>
       </c>
       <c r="D3" t="n">
-        <v>47.64912482561894</v>
+        <v>63.46508034103506</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.15157436154828</v>
+        <v>20.98191193516283</v>
       </c>
       <c r="C4" t="n">
-        <v>76.12962572581891</v>
+        <v>51.31889774409352</v>
       </c>
       <c r="D4" t="n">
-        <v>37.71383805864122</v>
+        <v>59.32112328140927</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.00940087088174</v>
+        <v>19.73312885536089</v>
       </c>
       <c r="C5" t="n">
-        <v>96.11310024576277</v>
+        <v>60.54928965942204</v>
       </c>
       <c r="D5" t="n">
-        <v>29.550605897829</v>
+        <v>37.7236555356837</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.07549676223577</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>60.90075533754239</v>
+        <v>48.7850069194325</v>
       </c>
       <c r="D6" t="n">
-        <v>30.51075515258238</v>
+        <v>32.48308629041422</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>26.76931465169778</v>
+        <v>24.79305652304895</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.63281066307846</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
         <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.045126400056638</v>
+        <v>7.047398083963379</v>
       </c>
       <c r="C21" t="n">
-        <v>66.04806000053098</v>
+        <v>66.06935703715668</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403204000035399</v>
+        <v>4.404623802477111</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.351105825221864</v>
+        <v>4.788965301315941</v>
       </c>
       <c r="C2" t="n">
-        <v>4.721224709722911</v>
+        <v>5.440845776935824</v>
       </c>
       <c r="D2" t="n">
-        <v>19.2216383014483</v>
+        <v>19.69680419030376</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.12306262039612</v>
+        <v>18.07397523518378</v>
       </c>
       <c r="C3" t="n">
-        <v>29.06464078422682</v>
+        <v>25.81505588316988</v>
       </c>
       <c r="D3" t="n">
-        <v>55.08095494676729</v>
+        <v>68.12347319768617</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.38428962518378</v>
+        <v>25.34676222824415</v>
       </c>
       <c r="C4" t="n">
-        <v>79.52450928710439</v>
+        <v>64.29858414194059</v>
       </c>
       <c r="D4" t="n">
-        <v>53.93525537591127</v>
+        <v>78.82255967856791</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.05973204570559</v>
+        <v>26.48264432205772</v>
       </c>
       <c r="C5" t="n">
-        <v>123.0620747273377</v>
+        <v>81.60777791551612</v>
       </c>
       <c r="D5" t="n">
-        <v>36.61918936840603</v>
+        <v>50.85453107998479</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.29312595740907</v>
+        <v>20.0855762811855</v>
       </c>
       <c r="C6" t="n">
-        <v>113.9926894355057</v>
+        <v>76.80015940781949</v>
       </c>
       <c r="D6" t="n">
-        <v>33.48937768726721</v>
+        <v>37.63529824230149</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.36038352291659</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>61.74309486778615</v>
+        <v>51.44259795482861</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>28.37250865273282</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>22.96406055003713</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,10 +6305,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.260130295853693</v>
+        <v>7.265907633870689</v>
       </c>
       <c r="C21" t="n">
-        <v>75.32385181948207</v>
+        <v>75.3837917014084</v>
       </c>
       <c r="D21" t="n">
-        <v>5.44509772189027</v>
+        <v>5.449430725403016</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.528401249063037</v>
+        <v>5.095270585040946</v>
       </c>
       <c r="C2" t="n">
-        <v>10.82278669161684</v>
+        <v>9.661379157492862</v>
       </c>
       <c r="D2" t="n">
-        <v>17.69992935986575</v>
+        <v>20.20142251028662</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.3608254912731</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="C3" t="n">
-        <v>22.7618205229623</v>
+        <v>23.02689240310894</v>
       </c>
       <c r="D3" t="n">
-        <v>57.43714943695964</v>
+        <v>68.07438581247384</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.91956310817654</v>
+        <v>30.6560538128109</v>
       </c>
       <c r="C4" t="n">
-        <v>75.69569324054183</v>
+        <v>64.52831310473435</v>
       </c>
       <c r="D4" t="n">
-        <v>68.05082386757191</v>
+        <v>95.29923139894213</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.42283982755667</v>
+        <v>32.96217917008666</v>
       </c>
       <c r="C5" t="n">
-        <v>136.2665813494573</v>
+        <v>101.7090621599696</v>
       </c>
       <c r="D5" t="n">
-        <v>47.73748211900116</v>
+        <v>67.66696051521141</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.5510068084565</v>
+        <v>28.41766904712818</v>
       </c>
       <c r="C6" t="n">
-        <v>156.297179759205</v>
+        <v>106.0228615724301</v>
       </c>
       <c r="D6" t="n">
-        <v>37.27303333943441</v>
+        <v>44.63908636439822</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>17.30723027816702</v>
       </c>
       <c r="C7" t="n">
-        <v>116.65911620024</v>
+        <v>84.02091377255476</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>56.57812019574367</v>
+        <v>49.31809592283852</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.06562253193106</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>34.06370009425158</v>
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.460963337526765</v>
+        <v>7.471813059013597</v>
       </c>
       <c r="C21" t="n">
-        <v>83.93583754717611</v>
+        <v>84.05789691390297</v>
       </c>
       <c r="D21" t="n">
-        <v>6.52834292033592</v>
+        <v>6.537836426636897</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_89_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449762790035</v>
+        <v>10.84497637385532</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907175649503</v>
+        <v>37.78907208700402</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.439864029231576</v>
+        <v>4.790928796724435</v>
       </c>
       <c r="C2" t="n">
-        <v>8.983973241562561</v>
+        <v>7.504479451262618</v>
       </c>
       <c r="D2" t="n">
-        <v>31.80273513137118</v>
+        <v>22.91791840793754</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.22967220953152</v>
+        <v>15.7128720064702</v>
       </c>
       <c r="C3" t="n">
-        <v>31.03304493124168</v>
+        <v>31.73008580125691</v>
       </c>
       <c r="D3" t="n">
-        <v>68.1283819362074</v>
+        <v>57.30952223540756</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.02166486941822</v>
+        <v>35.31444666946201</v>
       </c>
       <c r="C4" t="n">
-        <v>60.76331065894783</v>
+        <v>83.78725781894403</v>
       </c>
       <c r="D4" t="n">
-        <v>105.5987465641954</v>
+        <v>76.94643981575226</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.24536447726625</v>
+        <v>45.08676331753477</v>
       </c>
       <c r="C5" t="n">
-        <v>110.7656847316464</v>
+        <v>159.6567204031376</v>
       </c>
       <c r="D5" t="n">
-        <v>85.58385611771571</v>
+        <v>59.15029918087033</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.70951015719674</v>
+        <v>41.05668899160162</v>
       </c>
       <c r="C6" t="n">
-        <v>133.0317226639641</v>
+        <v>173.8871533761951</v>
       </c>
       <c r="D6" t="n">
-        <v>54.42023874180921</v>
+        <v>44.96109961139118</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.33203601268044</v>
+        <v>27.60772719112455</v>
       </c>
       <c r="C7" t="n">
-        <v>119.3540136483975</v>
+        <v>142.2905852627157</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>38.86640986342697</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.35176877775662</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>79.94371555681776</v>
+        <v>87.20373982972293</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>45.48437113775471</v>
+        <v>47.03749600587317</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
         <v>34.87658719336794</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.663455447751835</v>
+        <v>7.658271107859711</v>
       </c>
       <c r="C21" t="n">
-        <v>92.91939730399099</v>
+        <v>92.856537182799</v>
       </c>
       <c r="D21" t="n">
-        <v>7.663455447751835</v>
+        <v>7.658271107859711</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.412776004140166</v>
+        <v>5.836490101747288</v>
       </c>
       <c r="C2" t="n">
-        <v>16.09182662030947</v>
+        <v>9.986337647598555</v>
       </c>
       <c r="D2" t="n">
-        <v>34.95218176659494</v>
+        <v>29.65074416366217</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.57819264453914</v>
+        <v>15.69323705238526</v>
       </c>
       <c r="C3" t="n">
-        <v>32.80019079888594</v>
+        <v>30.24764676784423</v>
       </c>
       <c r="D3" t="n">
-        <v>75.90873249236338</v>
+        <v>60.87817514034471</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.28968199267759</v>
+        <v>32.57046183609218</v>
       </c>
       <c r="C4" t="n">
-        <v>68.86763795750525</v>
+        <v>81.43891731038566</v>
       </c>
       <c r="D4" t="n">
-        <v>114.0604300270987</v>
+        <v>84.9359026329128</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.92691836819179</v>
+        <v>48.22835597112457</v>
       </c>
       <c r="C5" t="n">
-        <v>110.127548723886</v>
+        <v>155.4352052748763</v>
       </c>
       <c r="D5" t="n">
-        <v>100.187353218387</v>
+        <v>70.98035901704441</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.9548082145382</v>
+        <v>49.54978838104078</v>
       </c>
       <c r="C6" t="n">
-        <v>153.1978022568978</v>
+        <v>210.2343986305247</v>
       </c>
       <c r="D6" t="n">
-        <v>66.85800040691205</v>
+        <v>51.40136455125026</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.59638818703009</v>
+        <v>36.89015173477814</v>
       </c>
       <c r="C7" t="n">
-        <v>151.9922160760827</v>
+        <v>189.8405535702057</v>
       </c>
       <c r="D7" t="n">
-        <v>46.59178254814513</v>
+        <v>42.57937968088841</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.86075605691297</v>
+        <v>20.9455872701057</v>
       </c>
       <c r="C8" t="n">
-        <v>115.4927999275948</v>
+        <v>132.8500993386784</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>70.44530651822986</v>
+        <v>73.55155625446676</v>
       </c>
       <c r="D9" t="n">
         <v>35.27812200440487</v>
@@ -1206,10 +1206,10 @@
         <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>41.42484438069417</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.839124850378125</v>
+        <v>7.828554954014987</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9287324486184</v>
+        <v>100.792645032943</v>
       </c>
       <c r="D21" t="n">
-        <v>8.819015456675391</v>
+        <v>8.80712432326686</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.825110039923826</v>
+        <v>6.437319696746336</v>
       </c>
       <c r="C2" t="n">
-        <v>17.3298104753647</v>
+        <v>10.0354250328109</v>
       </c>
       <c r="D2" t="n">
-        <v>31.33247798103695</v>
+        <v>24.73415166079414</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.92318699935727</v>
+        <v>16.95969159086365</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95070129727196</v>
+        <v>33.72794237939917</v>
       </c>
       <c r="D3" t="n">
-        <v>82.90859362364314</v>
+        <v>67.46570223584081</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.00890214926301</v>
+        <v>30.54118933141402</v>
       </c>
       <c r="C4" t="n">
-        <v>73.70470889632929</v>
+        <v>77.80154206615123</v>
       </c>
       <c r="D4" t="n">
-        <v>121.48833315743</v>
+        <v>92.91260272991813</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.8167826988669</v>
+        <v>48.08109381548755</v>
       </c>
       <c r="C5" t="n">
-        <v>115.9689475641545</v>
+        <v>152.661768010379</v>
       </c>
       <c r="D5" t="n">
-        <v>114.2999764669349</v>
+        <v>80.55239913345081</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.95230493978197</v>
+        <v>55.94980166502573</v>
       </c>
       <c r="C6" t="n">
-        <v>162.8984513225605</v>
+        <v>223.5576967248582</v>
       </c>
       <c r="D6" t="n">
-        <v>78.41022564278425</v>
+        <v>59.4516957260741</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.02232782195297</v>
+        <v>45.27427712904591</v>
       </c>
       <c r="C7" t="n">
-        <v>180.1988093667978</v>
+        <v>234.8752842594154</v>
       </c>
       <c r="D7" t="n">
-        <v>53.35896947351839</v>
+        <v>45.99291644855457</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.45319189093031</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="C8" t="n">
-        <v>151.0418842983718</v>
+        <v>180.4992241642973</v>
       </c>
       <c r="D8" t="n">
-        <v>41.55738032076748</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.86718632248619</v>
+        <v>14.31093628480575</v>
       </c>
       <c r="C9" t="n">
-        <v>101.2859288994392</v>
+        <v>110.8265530893096</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>58.2225476003571</v>
+        <v>59.64608177151497</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>38.91549724863931</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
         <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.998296834743764</v>
+        <v>7.981963900414102</v>
       </c>
       <c r="C21" t="n">
-        <v>108.9767943733838</v>
+        <v>107.7565126555904</v>
       </c>
       <c r="D21" t="n">
-        <v>9.997871043429704</v>
+        <v>9.977454875517628</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.33718143091316</v>
+        <v>5.965099051003619</v>
       </c>
       <c r="C2" t="n">
-        <v>11.92234412037327</v>
+        <v>7.064656479760047</v>
       </c>
       <c r="D2" t="n">
-        <v>25.86119802526948</v>
+        <v>20.43409671619311</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.25622045527519</v>
+        <v>20.41053477129119</v>
       </c>
       <c r="C3" t="n">
-        <v>65.78691366157877</v>
+        <v>50.11822030179967</v>
       </c>
       <c r="D3" t="n">
-        <v>89.96245087865647</v>
+        <v>72.50206795862695</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.5307089018368</v>
+        <v>23.10052348092745</v>
       </c>
       <c r="C4" t="n">
-        <v>97.50718198579321</v>
+        <v>117.2766355062112</v>
       </c>
       <c r="D4" t="n">
-        <v>120.3779765039269</v>
+        <v>89.5942954895639</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.12707172667112</v>
+        <v>31.51410130632262</v>
       </c>
       <c r="C5" t="n">
-        <v>97.34028487607128</v>
+        <v>133.5667751627786</v>
       </c>
       <c r="D5" t="n">
-        <v>77.55806863549803</v>
+        <v>57.16226007977055</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.43904651244335</v>
+        <v>28.09565580013523</v>
       </c>
       <c r="C6" t="n">
-        <v>118.6618815169035</v>
+        <v>154.6871135242402</v>
       </c>
       <c r="D6" t="n">
-        <v>35.13969557810609</v>
+        <v>30.26924521733767</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="C7" t="n">
-        <v>106.1789594574053</v>
+        <v>126.8997265032385</v>
       </c>
       <c r="D7" t="n">
-        <v>29.22466566001905</v>
+        <v>28.14670668075605</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>74.60300804571511</v>
+        <v>81.69613520889833</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>26.70353755551324</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>44.37499623195582</v>
+        <v>45.48437113775471</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
         <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.867104207028186</v>
+        <v>3.643265730459913</v>
       </c>
       <c r="C2" t="n">
-        <v>5.514476854754333</v>
+        <v>4.399211462729958</v>
       </c>
       <c r="D2" t="n">
-        <v>18.05826727191583</v>
+        <v>14.06157236792706</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.59001467471911</v>
+        <v>20.95540474714817</v>
       </c>
       <c r="C3" t="n">
-        <v>57.31443097392879</v>
+        <v>39.6282460819225</v>
       </c>
       <c r="D3" t="n">
-        <v>90.99328596811563</v>
+        <v>73.0567554115264</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.2093586073786</v>
+        <v>29.87752788334318</v>
       </c>
       <c r="C4" t="n">
-        <v>131.4560175986479</v>
+        <v>125.2150474427509</v>
       </c>
       <c r="D4" t="n">
-        <v>134.2127651521729</v>
+        <v>102.8292362905152</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.31775176547326</v>
+        <v>34.70478134512475</v>
       </c>
       <c r="C5" t="n">
-        <v>136.3402124272758</v>
+        <v>173.3766445699867</v>
       </c>
       <c r="D5" t="n">
-        <v>96.62851779049234</v>
+        <v>69.77771807934207</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.90698031447059</v>
+        <v>33.04660947265189</v>
       </c>
       <c r="C6" t="n">
-        <v>139.6732458831937</v>
+        <v>183.6683057536061</v>
       </c>
       <c r="D6" t="n">
-        <v>43.67304662341937</v>
+        <v>36.26674194258143</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>132.3494080095125</v>
+        <v>164.3288577276481</v>
       </c>
       <c r="D7" t="n">
-        <v>31.91956310817654</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>97.38446352276235</v>
+        <v>107.3982901060798</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>48.59062087399162</v>
+        <v>49.36718330805084</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
         <v>29.46715734296802</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.614795047036756</v>
+        <v>3.297690538565036</v>
       </c>
       <c r="C2" t="n">
-        <v>6.060328578315561</v>
+        <v>4.917574250572273</v>
       </c>
       <c r="D2" t="n">
-        <v>17.8373740384603</v>
+        <v>15.94063747385546</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.88744317137688</v>
+        <v>16.68480223367454</v>
       </c>
       <c r="C3" t="n">
-        <v>38.53850613020854</v>
+        <v>27.81782119983338</v>
       </c>
       <c r="D3" t="n">
-        <v>84.77882300023332</v>
+        <v>67.77004402415733</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.96534539737765</v>
+        <v>34.59973434077034</v>
       </c>
       <c r="C4" t="n">
-        <v>137.1481907878709</v>
+        <v>113.1542768960789</v>
       </c>
       <c r="D4" t="n">
-        <v>146.8350953856742</v>
+        <v>113.9200401053914</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.60093707265284</v>
+        <v>39.26990816987242</v>
       </c>
       <c r="C5" t="n">
-        <v>188.4710155227814</v>
+        <v>200.1783568959247</v>
       </c>
       <c r="D5" t="n">
-        <v>118.4724042099839</v>
+        <v>87.30191460014763</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.66296710446964</v>
+        <v>38.9233512302733</v>
       </c>
       <c r="C6" t="n">
-        <v>174.6116831819292</v>
+        <v>225.4092728950677</v>
       </c>
       <c r="D6" t="n">
-        <v>59.61270234957058</v>
+        <v>47.01393406097126</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.59532432386784</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="C7" t="n">
-        <v>165.346930096952</v>
+        <v>211.75905281522</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C8" t="n">
-        <v>132.3494080095125</v>
+        <v>156.0487975900305</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>78.32186834940201</v>
+        <v>83.6468678972367</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2481,7 +2481,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.189297380470387</v>
+        <v>2.011601046001715</v>
       </c>
       <c r="C2" t="n">
-        <v>2.926589906359742</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="D2" t="n">
-        <v>12.45052438525805</v>
+        <v>11.12320148911636</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3131207643925</v>
+        <v>16.06630117999905</v>
       </c>
       <c r="C3" t="n">
-        <v>34.48388811166921</v>
+        <v>26.02613163958294</v>
       </c>
       <c r="D3" t="n">
-        <v>83.3356538749905</v>
+        <v>67.49024592844698</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.36022895866312</v>
+        <v>38.05843150283185</v>
       </c>
       <c r="C4" t="n">
-        <v>137.0716144669396</v>
+        <v>109.1084946068778</v>
       </c>
       <c r="D4" t="n">
-        <v>156.368847341615</v>
+        <v>121.730824840379</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.53359739168732</v>
+        <v>40.79161711145498</v>
       </c>
       <c r="C5" t="n">
-        <v>231.6188271244288</v>
+        <v>235.693080097053</v>
       </c>
       <c r="D5" t="n">
-        <v>124.6328710541326</v>
+        <v>92.35791527701869</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.82018560586937</v>
+        <v>31.396291581813</v>
       </c>
       <c r="C6" t="n">
-        <v>208.0205575574482</v>
+        <v>265.4596704898163</v>
       </c>
       <c r="D6" t="n">
-        <v>57.92213280285758</v>
+        <v>46.49066253460771</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>172.0542304123663</v>
+        <v>213.7353109438688</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>96.63342652901355</v>
+        <v>107.4817386609408</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
         <v>31.39530983410874</v>
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2778,7 +2778,7 @@
         <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.176534660315179</v>
+        <v>3.199515768140355</v>
       </c>
       <c r="C2" t="n">
-        <v>7.767587836000764</v>
+        <v>8.58145668282137</v>
       </c>
       <c r="D2" t="n">
-        <v>16.62786086682823</v>
+        <v>10.22097534891354</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.64491043069892</v>
+        <v>11.70243263462198</v>
       </c>
       <c r="C3" t="n">
-        <v>23.16433708170349</v>
+        <v>17.70581984609123</v>
       </c>
       <c r="D3" t="n">
-        <v>75.16751297565703</v>
+        <v>61.5408548407113</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.70558316637975</v>
+        <v>34.59973434077034</v>
       </c>
       <c r="C4" t="n">
-        <v>112.8224461720434</v>
+        <v>88.79024411978578</v>
       </c>
       <c r="D4" t="n">
-        <v>160.8740875564036</v>
+        <v>126.2743532156332</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.82936549257286</v>
+        <v>47.81111319681967</v>
       </c>
       <c r="C5" t="n">
-        <v>242.8352946454486</v>
+        <v>221.8749811597792</v>
       </c>
       <c r="D5" t="n">
-        <v>146.1822331623501</v>
+        <v>109.9557428756428</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.19253002768617</v>
+        <v>40.6139207769863</v>
       </c>
       <c r="C6" t="n">
-        <v>277.494915596178</v>
+        <v>314.5264390003676</v>
       </c>
       <c r="D6" t="n">
-        <v>77.40393424593128</v>
+        <v>60.41773546705297</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.9897248590678</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C7" t="n">
-        <v>227.8685508942059</v>
+        <v>285.0003767951448</v>
       </c>
       <c r="D7" t="n">
-        <v>41.26187426178919</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>147.5370449942107</v>
+        <v>176.6605906406923</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>32.71183350550372</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>62.79061966821748</v>
+        <v>68.44843168779184</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.524654184695297</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C2" t="n">
-        <v>4.217588137444298</v>
+        <v>5.456553740203772</v>
       </c>
       <c r="D2" t="n">
-        <v>12.39652826152447</v>
+        <v>7.670394813280329</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.62741889847172</v>
+        <v>11.42754327743287</v>
       </c>
       <c r="C3" t="n">
-        <v>26.69862881699201</v>
+        <v>24.78422079371073</v>
       </c>
       <c r="D3" t="n">
-        <v>72.08973392284329</v>
+        <v>57.11808143307943</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.54493639578177</v>
+        <v>30.79644373451819</v>
       </c>
       <c r="C4" t="n">
-        <v>92.44038208417543</v>
+        <v>72.6709285637574</v>
       </c>
       <c r="D4" t="n">
-        <v>161.8312915680442</v>
+        <v>127.8569305148791</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.12451169865266</v>
+        <v>50.78090000216628</v>
       </c>
       <c r="C5" t="n">
-        <v>238.1474493576701</v>
+        <v>208.1059696077177</v>
       </c>
       <c r="D5" t="n">
-        <v>161.7674779672682</v>
+        <v>122.7430067234575</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.14977509705582</v>
+        <v>47.17494068446774</v>
       </c>
       <c r="C6" t="n">
-        <v>324.0660814425339</v>
+        <v>342.0988232741394</v>
       </c>
       <c r="D6" t="n">
-        <v>90.44547074914593</v>
+        <v>70.07813287684159</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.19312656029614</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C7" t="n">
-        <v>285.0602634051039</v>
+        <v>342.8508420155924</v>
       </c>
       <c r="D7" t="n">
-        <v>46.35223610830891</v>
+        <v>41.32176087174825</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>186.5075201142878</v>
+        <v>229.31662875797</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>68.89218165011141</v>
+        <v>75.32655610374501</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.265292864324891</v>
+        <v>2.745948328778329</v>
       </c>
       <c r="C2" t="n">
-        <v>4.722206457427157</v>
+        <v>11.08884031946772</v>
       </c>
       <c r="D2" t="n">
-        <v>18.23989059720149</v>
+        <v>14.87740471015616</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.109236037078654</v>
+        <v>9.400234268163208</v>
       </c>
       <c r="C3" t="n">
-        <v>21.94696992843745</v>
+        <v>22.94344384824796</v>
       </c>
       <c r="D3" t="n">
-        <v>66.4545021004666</v>
+        <v>51.75773896789184</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.85276320655876</v>
+        <v>26.69961056469625</v>
       </c>
       <c r="C4" t="n">
-        <v>81.22195106774711</v>
+        <v>67.75728130400211</v>
       </c>
       <c r="D4" t="n">
-        <v>160.35081603004</v>
+        <v>125.5085900063207</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.58455046131692</v>
+        <v>48.98921044191585</v>
       </c>
       <c r="C5" t="n">
-        <v>209.9958339383928</v>
+        <v>176.8618489200629</v>
       </c>
       <c r="D5" t="n">
-        <v>173.9411494999287</v>
+        <v>135.5548142638784</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.56237117474674</v>
+        <v>54.90325861229863</v>
       </c>
       <c r="C6" t="n">
-        <v>345.7214723028101</v>
+        <v>338.9591941159581</v>
       </c>
       <c r="D6" t="n">
-        <v>111.0945702125691</v>
+        <v>85.53476873250337</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.930902112271</v>
+        <v>28.20659329071511</v>
       </c>
       <c r="C7" t="n">
-        <v>354.4688443476491</v>
+        <v>406.270761962232</v>
       </c>
       <c r="D7" t="n">
-        <v>56.23352675155305</v>
+        <v>48.26860762699867</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.34347282776614</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>258.4401744044516</v>
+        <v>311.930698070339</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>123.2515520342573</v>
+        <v>147.9906124335726</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>47.68839473378882</v>
+        <v>50.25075624187299</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -3711,7 +3711,7 @@
         <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3725,7 +3725,7 @@
         <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.522911673465055</v>
+        <v>5.310273332270997</v>
       </c>
       <c r="C2" t="n">
-        <v>9.337402415091415</v>
+        <v>10.3584200275081</v>
       </c>
       <c r="D2" t="n">
-        <v>21.04474378823463</v>
+        <v>12.7411217057151</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.384665173615502</v>
+        <v>2.00669230748048</v>
       </c>
       <c r="C2" t="n">
-        <v>2.795035713990669</v>
+        <v>6.476589604916207</v>
       </c>
       <c r="D2" t="n">
-        <v>13.56971676809941</v>
+        <v>11.06822361767854</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.51590057081509</v>
+        <v>12.40929098167968</v>
       </c>
       <c r="C3" t="n">
-        <v>24.5927799913826</v>
+        <v>32.01479263548849</v>
       </c>
       <c r="D3" t="n">
-        <v>73.63598655703201</v>
+        <v>57.55986789999049</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.00738062221102</v>
+        <v>37.17780381212246</v>
       </c>
       <c r="C4" t="n">
-        <v>118.2593649581623</v>
+        <v>100.2128786586974</v>
       </c>
       <c r="D4" t="n">
-        <v>163.3245298262036</v>
+        <v>127.7548287536374</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.50151851261666</v>
+        <v>31.3668391506856</v>
       </c>
       <c r="C5" t="n">
-        <v>300.4393411921302</v>
+        <v>278.1291246131214</v>
       </c>
       <c r="D5" t="n">
-        <v>159.0922154731956</v>
+        <v>123.6511233498858</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.1006623496477</v>
+        <v>17.50947030524187</v>
       </c>
       <c r="C6" t="n">
-        <v>294.4408627191822</v>
+        <v>327.3667172242118</v>
       </c>
       <c r="D6" t="n">
-        <v>85.93728529124456</v>
+        <v>68.70957657712154</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.850815406683489</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>181.7558612257332</v>
+        <v>219.36465228002</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>90.79202768874502</v>
+        <v>109.0672612032994</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>19.85781081380023</v>
       </c>
     </row>
     <row r="10">
@@ -4319,7 +4319,7 @@
         <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4333,7 +4333,7 @@
         <v>15.28188476430585</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.54040320569225</v>
+        <v>6.135923151542564</v>
       </c>
       <c r="C2" t="n">
-        <v>5.225843029705771</v>
+        <v>5.062872910800801</v>
       </c>
       <c r="D2" t="n">
-        <v>23.55998140651495</v>
+        <v>12.80002656796991</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.611310024576275</v>
+        <v>11.28518986031709</v>
       </c>
       <c r="C3" t="n">
-        <v>23.52758373227481</v>
+        <v>26.09976271740146</v>
       </c>
       <c r="D3" t="n">
-        <v>20.81305133003238</v>
+        <v>13.83773389135879</v>
       </c>
     </row>
     <row r="4">
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4585,7 +4585,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
         <v>32.21899615797182</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39601475374789</v>
+        <v>13.39712574109244</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13207724020955</v>
+        <v>70.13789358571923</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576001735735046</v>
+        <v>1.576132440128522</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.508185457901353</v>
+        <v>5.224861282001525</v>
       </c>
       <c r="C2" t="n">
-        <v>6.467753875577987</v>
+        <v>9.997136872345271</v>
       </c>
       <c r="D2" t="n">
-        <v>20.91122610045706</v>
+        <v>17.03528616409065</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.35239067256238</v>
+        <v>17.22476347101029</v>
       </c>
       <c r="C3" t="n">
-        <v>21.55917958525995</v>
+        <v>22.12368451520187</v>
       </c>
       <c r="D3" t="n">
-        <v>35.57362806338318</v>
+        <v>21.24502031990098</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.29500733735955</v>
+        <v>13.18388992033042</v>
       </c>
       <c r="C4" t="n">
-        <v>36.39927788265474</v>
+        <v>40.31743297030376</v>
       </c>
       <c r="D4" t="n">
-        <v>25.97213551584937</v>
+        <v>22.32199755145973</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
         <v>36.63391558396972</v>
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43514992269241</v>
+        <v>15.43895121958327</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11188904238924</v>
+        <v>86.13309627767511</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249505246882612</v>
+        <v>3.250305519912268</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.383503499462008</v>
+        <v>6.140831890063798</v>
       </c>
       <c r="C2" t="n">
-        <v>7.768569583705011</v>
+        <v>11.14479993860979</v>
       </c>
       <c r="D2" t="n">
-        <v>32.73048671188441</v>
+        <v>18.56190384419444</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.3755517068368</v>
+        <v>17.72054606165493</v>
       </c>
       <c r="C3" t="n">
-        <v>23.69448084199677</v>
+        <v>32.29949946972006</v>
       </c>
       <c r="D3" t="n">
-        <v>44.04611075103315</v>
+        <v>29.94330497952772</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.930100291016</v>
+        <v>24.64481261970768</v>
       </c>
       <c r="C4" t="n">
-        <v>46.22657240216531</v>
+        <v>49.21304891848411</v>
       </c>
       <c r="D4" t="n">
-        <v>37.94356702143497</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.21017612416683</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="C5" t="n">
-        <v>40.66889864842413</v>
+        <v>44.76769531365456</v>
       </c>
       <c r="D5" t="n">
-        <v>31.95588777323368</v>
+        <v>30.67961575771283</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.39751000922872</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.2069942013426</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5235,10 +5235,10 @@
         <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72369910844792</v>
+        <v>16.72976640419939</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0145645615323</v>
+        <v>102.0515750656163</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180924777111979</v>
+        <v>4.182441601049848</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.820381227851839</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C2" t="n">
-        <v>8.746390297134834</v>
+        <v>11.8182788637231</v>
       </c>
       <c r="D2" t="n">
-        <v>28.27237038689964</v>
+        <v>17.49278059426967</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.59506228196058</v>
+        <v>19.44842202112931</v>
       </c>
       <c r="C3" t="n">
-        <v>27.32203860918873</v>
+        <v>38.60722846950582</v>
       </c>
       <c r="D3" t="n">
-        <v>59.12084674974292</v>
+        <v>37.38986131623977</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.89930625928586</v>
+        <v>29.5967480399286</v>
       </c>
       <c r="C4" t="n">
-        <v>52.93976320380501</v>
+        <v>66.87665361329272</v>
       </c>
       <c r="D4" t="n">
-        <v>50.75733805726435</v>
+        <v>36.1950743601714</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.99743997198154</v>
+        <v>24.32279937271473</v>
       </c>
       <c r="C5" t="n">
-        <v>64.81989217289566</v>
+        <v>69.67954330891737</v>
       </c>
       <c r="D5" t="n">
-        <v>37.74819922828986</v>
+        <v>33.4285093296039</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.821404033285093</v>
+        <v>10.78744377426395</v>
       </c>
       <c r="C6" t="n">
-        <v>39.36611944488861</v>
+        <v>42.54600025894403</v>
       </c>
       <c r="D6" t="n">
-        <v>38.76234460677682</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04067164330244</v>
+        <v>18.04995237583614</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6939054824968</v>
+        <v>117.7544512137882</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013557214434145</v>
+        <v>6.01665079194538</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.887540982368122</v>
+        <v>6.440264939859076</v>
       </c>
       <c r="C2" t="n">
-        <v>6.12512392679585</v>
+        <v>11.20272305316035</v>
       </c>
       <c r="D2" t="n">
-        <v>23.80443658487241</v>
+        <v>25.98686173141307</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.25497666566369</v>
+        <v>17.04804888424586</v>
       </c>
       <c r="C3" t="n">
-        <v>29.13827186204533</v>
+        <v>40.0602150717911</v>
       </c>
       <c r="D3" t="n">
-        <v>63.46508034103506</v>
+        <v>39.85895679242051</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.98191193516283</v>
+        <v>24.49165997784518</v>
       </c>
       <c r="C4" t="n">
-        <v>51.31889774409352</v>
+        <v>69.04631603967817</v>
       </c>
       <c r="D4" t="n">
-        <v>59.32112328140927</v>
+        <v>40.30467025014855</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.73312885536089</v>
+        <v>20.91122610045706</v>
       </c>
       <c r="C5" t="n">
-        <v>60.54928965942204</v>
+        <v>73.21383504420589</v>
       </c>
       <c r="D5" t="n">
-        <v>37.7236555356837</v>
+        <v>31.04777114680538</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.14970867713103</v>
+        <v>11.91449013873929</v>
       </c>
       <c r="C6" t="n">
-        <v>48.7850069194325</v>
+        <v>52.5284109157256</v>
       </c>
       <c r="D6" t="n">
-        <v>32.48308629041422</v>
+        <v>31.35603992593888</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>24.79305652304895</v>
+        <v>26.23033516206628</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
         <v>30.28593492830985</v>
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>18.99190933865455</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.047398083963379</v>
+        <v>7.051343316756977</v>
       </c>
       <c r="C21" t="n">
-        <v>66.06935703715668</v>
+        <v>66.10634359459667</v>
       </c>
       <c r="D21" t="n">
-        <v>4.404623802477111</v>
+        <v>4.407089572973111</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.788965301315941</v>
+        <v>4.806636759992384</v>
       </c>
       <c r="C2" t="n">
-        <v>5.440845776935824</v>
+        <v>5.112942043717388</v>
       </c>
       <c r="D2" t="n">
-        <v>19.69680419030376</v>
+        <v>20.45765866109504</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.07397523518378</v>
+        <v>20.36635612460008</v>
       </c>
       <c r="C3" t="n">
-        <v>25.81505588316988</v>
+        <v>42.39186586937728</v>
       </c>
       <c r="D3" t="n">
-        <v>68.12347319768617</v>
+        <v>52.05717201768712</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.34676222824415</v>
+        <v>30.06896868567131</v>
       </c>
       <c r="C4" t="n">
-        <v>64.29858414194059</v>
+        <v>88.49670155621598</v>
       </c>
       <c r="D4" t="n">
-        <v>78.82255967856791</v>
+        <v>51.84216927045707</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.48264432205772</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="C5" t="n">
-        <v>81.60777791551612</v>
+        <v>105.9796646734432</v>
       </c>
       <c r="D5" t="n">
-        <v>50.85453107998479</v>
+        <v>38.7054032399305</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.0855762811855</v>
+        <v>21.01136436629024</v>
       </c>
       <c r="C6" t="n">
-        <v>76.80015940781949</v>
+        <v>88.9561594818035</v>
       </c>
       <c r="D6" t="n">
-        <v>37.63529824230149</v>
+        <v>34.65667570761666</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.701630813366979</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>51.44259795482861</v>
+        <v>55.21545438224911</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>27.12078032981814</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -6165,7 +6165,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
         <v>23.18593553119691</v>
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.265907633870689</v>
+        <v>7.268624319560762</v>
       </c>
       <c r="C21" t="n">
-        <v>75.3837917014084</v>
+        <v>75.41197731544291</v>
       </c>
       <c r="D21" t="n">
-        <v>5.449430725403016</v>
+        <v>5.451468239670572</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.095270585040946</v>
+        <v>3.981968688425063</v>
       </c>
       <c r="C2" t="n">
-        <v>9.661379157492862</v>
+        <v>8.798422925459915</v>
       </c>
       <c r="D2" t="n">
-        <v>20.20142251028662</v>
+        <v>18.34788284466864</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.20021977840412</v>
+        <v>18.25068982194821</v>
       </c>
       <c r="C3" t="n">
-        <v>23.02689240310894</v>
+        <v>29.15299807760903</v>
       </c>
       <c r="D3" t="n">
-        <v>68.07438581247384</v>
+        <v>56.02343274284423</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.6560538128109</v>
+        <v>35.48036203147973</v>
       </c>
       <c r="C4" t="n">
-        <v>64.52831310473435</v>
+        <v>97.68586006796613</v>
       </c>
       <c r="D4" t="n">
-        <v>95.29923139894213</v>
+        <v>64.98777103032187</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.96217917008666</v>
+        <v>37.94454876913922</v>
       </c>
       <c r="C5" t="n">
-        <v>101.7090621599696</v>
+        <v>138.2791641431633</v>
       </c>
       <c r="D5" t="n">
-        <v>67.66696051521141</v>
+        <v>48.64559874542947</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.41766904712818</v>
+        <v>31.55729820530948</v>
       </c>
       <c r="C6" t="n">
-        <v>106.0228615724301</v>
+        <v>131.9449279553629</v>
       </c>
       <c r="D6" t="n">
-        <v>44.63908636439822</v>
+        <v>38.80259626265094</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>84.02091377255476</v>
+        <v>94.44118390543041</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>49.31809592283852</v>
+        <v>51.7381040138069</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6524,7 +6524,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.471813059013597</v>
+        <v>7.471330400707015</v>
       </c>
       <c r="C21" t="n">
-        <v>84.05789691390297</v>
+        <v>84.05246700795392</v>
       </c>
       <c r="D21" t="n">
-        <v>6.537836426636897</v>
+        <v>6.537414100618639</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_89_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497637385532</v>
+        <v>10.84497643065658</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907208700402</v>
+        <v>37.78907228492671</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.790928796724435</v>
+        <v>1.331249886958675</v>
       </c>
       <c r="C2" t="n">
-        <v>7.504479451262618</v>
+        <v>2.021418523044182</v>
       </c>
       <c r="D2" t="n">
-        <v>22.91791840793754</v>
+        <v>10.89052728320987</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.7128720064702</v>
+        <v>11.68770641905828</v>
       </c>
       <c r="C3" t="n">
-        <v>31.73008580125691</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D3" t="n">
-        <v>57.30952223540756</v>
+        <v>54.13356841216913</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.31444666946201</v>
+        <v>20.53521672973053</v>
       </c>
       <c r="C4" t="n">
-        <v>83.78725781894403</v>
+        <v>100.4808957819568</v>
       </c>
       <c r="D4" t="n">
-        <v>76.94643981575226</v>
+        <v>64.19648238069892</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.08676331753477</v>
+        <v>19.38951715887451</v>
       </c>
       <c r="C5" t="n">
-        <v>159.6567204031376</v>
+        <v>109.5139564087317</v>
       </c>
       <c r="D5" t="n">
-        <v>59.15029918087033</v>
+        <v>42.80419990516094</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.05668899160162</v>
+        <v>12.63901994447344</v>
       </c>
       <c r="C6" t="n">
-        <v>173.8871533761951</v>
+        <v>58.88817254383644</v>
       </c>
       <c r="D6" t="n">
-        <v>44.96109961139118</v>
+        <v>29.86672865859647</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.60772719112455</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>142.2905852627157</v>
+        <v>35.39298648580176</v>
       </c>
       <c r="D7" t="n">
-        <v>38.86640986342697</v>
+        <v>29.52409870981433</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>87.20373982972293</v>
+        <v>28.37250865273282</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>47.03749600587317</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.658271107859711</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.856537182799</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.658271107859711</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.836490101747288</v>
+        <v>0.9915651812892784</v>
       </c>
       <c r="C2" t="n">
-        <v>9.986337647598555</v>
+        <v>5.947427592327178</v>
       </c>
       <c r="D2" t="n">
-        <v>29.65074416366217</v>
+        <v>12.60367702712055</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.69323705238526</v>
+        <v>7.883434065101888</v>
       </c>
       <c r="C3" t="n">
-        <v>30.24764676784423</v>
+        <v>16.6357148484622</v>
       </c>
       <c r="D3" t="n">
-        <v>60.87817514034471</v>
+        <v>50.28511741152163</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.57046183609218</v>
+        <v>21.78596330494097</v>
       </c>
       <c r="C4" t="n">
-        <v>81.43891731038566</v>
+        <v>85.03800439415447</v>
       </c>
       <c r="D4" t="n">
-        <v>84.9359026329128</v>
+        <v>76.93367709559706</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.22835597112457</v>
+        <v>25.69724615866027</v>
       </c>
       <c r="C5" t="n">
-        <v>155.4352052748763</v>
+        <v>153.2753603255333</v>
       </c>
       <c r="D5" t="n">
-        <v>70.98035901704441</v>
+        <v>56.20505606812991</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.54978838104078</v>
+        <v>19.28054316370311</v>
       </c>
       <c r="C6" t="n">
-        <v>210.2343986305247</v>
+        <v>120.2316960959941</v>
       </c>
       <c r="D6" t="n">
-        <v>51.40136455125026</v>
+        <v>36.70951015719674</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.89015173477814</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>189.8405535702057</v>
+        <v>61.26400198811371</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.9455872701057</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>132.8500993386784</v>
+        <v>38.21943812632832</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>73.55155625446676</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>42.27896488338889</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.828554954014987</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.792645032943</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.80712432326686</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.437319696746336</v>
+        <v>0.512472301616835</v>
       </c>
       <c r="C2" t="n">
-        <v>10.0354250328109</v>
+        <v>2.43473430653209</v>
       </c>
       <c r="D2" t="n">
-        <v>24.73415166079414</v>
+        <v>8.505862109594364</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.95969159086365</v>
+        <v>6.798602851909163</v>
       </c>
       <c r="C3" t="n">
-        <v>33.72794237939917</v>
+        <v>21.15666302651876</v>
       </c>
       <c r="D3" t="n">
-        <v>67.46570223584081</v>
+        <v>50.54528055314703</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.54118933141402</v>
+        <v>23.7769476491535</v>
       </c>
       <c r="C4" t="n">
-        <v>77.80154206615123</v>
+        <v>74.57257386688347</v>
       </c>
       <c r="D4" t="n">
-        <v>92.91260272991813</v>
+        <v>84.47644470732529</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.08109381548755</v>
+        <v>25.84450831429729</v>
       </c>
       <c r="C5" t="n">
-        <v>152.661768010379</v>
+        <v>175.0947030524187</v>
       </c>
       <c r="D5" t="n">
-        <v>80.55239913345081</v>
+        <v>64.45173678380311</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.94980166502573</v>
+        <v>15.29562923216531</v>
       </c>
       <c r="C6" t="n">
-        <v>223.5576967248582</v>
+        <v>159.678318852631</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4516957260741</v>
+        <v>37.27303333943441</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.27427712904591</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C7" t="n">
-        <v>234.8752842594154</v>
+        <v>61.32388859807276</v>
       </c>
       <c r="D7" t="n">
-        <v>45.99291644855457</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.20561154301086</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>180.4992241642973</v>
+        <v>39.80496066868692</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.31093628480575</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>110.8265530893096</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>36.27655941962388</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>59.64608177151497</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91549724863931</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.981963900414102</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7565126555904</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.977454875517628</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.965099051003619</v>
+        <v>0.4663301595172349</v>
       </c>
       <c r="C2" t="n">
-        <v>7.064656479760047</v>
+        <v>5.39274013942773</v>
       </c>
       <c r="D2" t="n">
-        <v>20.43409671619311</v>
+        <v>12.41910845872215</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.41053477129119</v>
+        <v>4.147884050442774</v>
       </c>
       <c r="C3" t="n">
-        <v>50.11822030179967</v>
+        <v>14.37769512869454</v>
       </c>
       <c r="D3" t="n">
-        <v>72.50206795862695</v>
+        <v>45.76416923346507</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.10052348092745</v>
+        <v>18.51870694520758</v>
       </c>
       <c r="C4" t="n">
-        <v>117.2766355062112</v>
+        <v>63.02231212641975</v>
       </c>
       <c r="D4" t="n">
-        <v>89.5942954895639</v>
+        <v>90.46216046011808</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.51410130632262</v>
+        <v>31.39138284329177</v>
       </c>
       <c r="C5" t="n">
-        <v>133.5667751627786</v>
+        <v>158.3804483876167</v>
       </c>
       <c r="D5" t="n">
-        <v>57.16226007977055</v>
+        <v>80.03698158872123</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.09565580013523</v>
+        <v>24.0704902127233</v>
       </c>
       <c r="C6" t="n">
-        <v>154.6871135242402</v>
+        <v>220.7400808136699</v>
       </c>
       <c r="D6" t="n">
-        <v>30.26924521733767</v>
+        <v>47.25544399621598</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>126.8997265032385</v>
+        <v>143.667977291774</v>
       </c>
       <c r="D7" t="n">
-        <v>28.14670668075605</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>81.69613520889833</v>
+        <v>60.16640805476577</v>
       </c>
       <c r="D8" t="n">
-        <v>26.70353755551324</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>45.48437113775471</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>24.00864010735575</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.643265730459913</v>
+        <v>0.2493639168786898</v>
       </c>
       <c r="C2" t="n">
-        <v>4.399211462729958</v>
+        <v>3.61675854244525</v>
       </c>
       <c r="D2" t="n">
-        <v>14.06157236792706</v>
+        <v>8.526478811383548</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.95540474714817</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C3" t="n">
-        <v>39.6282460819225</v>
+        <v>18.32922963828795</v>
       </c>
       <c r="D3" t="n">
-        <v>73.0567554115264</v>
+        <v>45.84270904980481</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.87752788334318</v>
+        <v>14.60055185755856</v>
       </c>
       <c r="C4" t="n">
-        <v>125.2150474427509</v>
+        <v>51.21679598285185</v>
       </c>
       <c r="D4" t="n">
-        <v>102.8292362905152</v>
+        <v>92.95089089038376</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.70478134512475</v>
+        <v>32.2749557771139</v>
       </c>
       <c r="C5" t="n">
-        <v>173.3766445699867</v>
+        <v>145.1023106876786</v>
       </c>
       <c r="D5" t="n">
-        <v>69.77771807934207</v>
+        <v>91.74432296186444</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.04660947265189</v>
+        <v>30.10823859384119</v>
       </c>
       <c r="C6" t="n">
-        <v>183.6683057536061</v>
+        <v>246.5011405731062</v>
       </c>
       <c r="D6" t="n">
-        <v>36.26674194258143</v>
+        <v>56.43282153551517</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>11.43834250217959</v>
       </c>
       <c r="C7" t="n">
-        <v>164.3288577276481</v>
+        <v>209.5432482467349</v>
       </c>
       <c r="D7" t="n">
-        <v>30.48228446915921</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>107.3982901060798</v>
+        <v>95.63204387068178</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>49.36718330805084</v>
+        <v>49.14530832689106</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.297690538565036</v>
+        <v>0.9709484795000954</v>
       </c>
       <c r="C2" t="n">
-        <v>4.917574250572273</v>
+        <v>6.456954650831271</v>
       </c>
       <c r="D2" t="n">
-        <v>15.94063747385546</v>
+        <v>10.73148415512189</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.68480223367454</v>
+        <v>1.91440802328128</v>
       </c>
       <c r="C3" t="n">
-        <v>27.81782119983338</v>
+        <v>15.96812640957437</v>
       </c>
       <c r="D3" t="n">
-        <v>67.77004402415733</v>
+        <v>42.22496875965532</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.59973434077034</v>
+        <v>10.26122700478766</v>
       </c>
       <c r="C4" t="n">
-        <v>113.1542768960789</v>
+        <v>48.37070938824035</v>
       </c>
       <c r="D4" t="n">
-        <v>113.9200401053914</v>
+        <v>94.64833267102649</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.26990816987242</v>
+        <v>28.34796496012666</v>
       </c>
       <c r="C5" t="n">
-        <v>200.1783568959247</v>
+        <v>121.0985793188441</v>
       </c>
       <c r="D5" t="n">
-        <v>87.30191460014763</v>
+        <v>103.1325963311275</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.9233512302733</v>
+        <v>36.4277485660779</v>
       </c>
       <c r="C6" t="n">
-        <v>225.4092728950677</v>
+        <v>240.2218822567436</v>
       </c>
       <c r="D6" t="n">
-        <v>47.01393406097126</v>
+        <v>70.11838453271571</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.69135567243478</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="C7" t="n">
-        <v>211.75905281522</v>
+        <v>280.8083140980109</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>46.65166915810418</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>156.0487975900305</v>
+        <v>177.3281790795801</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29044275620359</v>
+        <v>42.39186586937727</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>83.6468678972367</v>
+        <v>79.32030576462103</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>43.04374634499714</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>43.56014563743098</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.011601046001715</v>
+        <v>0.6440264939859075</v>
       </c>
       <c r="C2" t="n">
-        <v>2.405281875404686</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D2" t="n">
-        <v>11.12320148911636</v>
+        <v>7.726354432422397</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.06630117999905</v>
+        <v>3.333033455917922</v>
       </c>
       <c r="C3" t="n">
-        <v>26.02613163958294</v>
+        <v>21.86352137357647</v>
       </c>
       <c r="D3" t="n">
-        <v>67.49024592844698</v>
+        <v>45.81816535719864</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.05843150283185</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="C4" t="n">
-        <v>109.1084946068778</v>
+        <v>68.71448531564275</v>
       </c>
       <c r="D4" t="n">
-        <v>121.730824840379</v>
+        <v>99.6002680912474</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.79161711145498</v>
+        <v>22.87472150895069</v>
       </c>
       <c r="C5" t="n">
-        <v>235.693080097053</v>
+        <v>191.9562198728576</v>
       </c>
       <c r="D5" t="n">
-        <v>92.35791527701869</v>
+        <v>97.31574118346511</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.396291581813</v>
+        <v>13.20254312671111</v>
       </c>
       <c r="C6" t="n">
-        <v>265.4596704898163</v>
+        <v>248.5137233668121</v>
       </c>
       <c r="D6" t="n">
-        <v>46.49066253460771</v>
+        <v>61.82654342264714</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>213.7353109438688</v>
+        <v>124.6839219347534</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>107.4817386609408</v>
+        <v>58.41398840268521</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
         <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.199515768140355</v>
+        <v>0.3239767424014474</v>
       </c>
       <c r="C2" t="n">
-        <v>8.58145668282137</v>
+        <v>2.438661297349077</v>
       </c>
       <c r="D2" t="n">
-        <v>10.22097534891354</v>
+        <v>5.809982913732624</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.70243263462198</v>
+        <v>2.783254741539707</v>
       </c>
       <c r="C3" t="n">
-        <v>17.70581984609123</v>
+        <v>16.80752069670539</v>
       </c>
       <c r="D3" t="n">
-        <v>61.5408548407113</v>
+        <v>41.37084825696059</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.59973434077034</v>
+        <v>11.69065166217102</v>
       </c>
       <c r="C4" t="n">
-        <v>88.79024411978578</v>
+        <v>59.30836056125406</v>
       </c>
       <c r="D4" t="n">
-        <v>126.2743532156332</v>
+        <v>96.95838501911925</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.81111319681967</v>
+        <v>20.54307071136451</v>
       </c>
       <c r="C5" t="n">
-        <v>221.8749811597792</v>
+        <v>144.6850679133737</v>
       </c>
       <c r="D5" t="n">
-        <v>109.9557428756428</v>
+        <v>98.93562489547234</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.6139207769863</v>
+        <v>13.4038014060817</v>
       </c>
       <c r="C6" t="n">
-        <v>314.5264390003676</v>
+        <v>229.2734318589832</v>
       </c>
       <c r="D6" t="n">
-        <v>60.41773546705297</v>
+        <v>64.64415933383549</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>285.0003767951448</v>
+        <v>169.7785392339221</v>
       </c>
       <c r="D7" t="n">
-        <v>37.36924461445059</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>176.6605906406923</v>
+        <v>67.84367510197582</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>68.44843168779184</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.135301256736813</v>
+        <v>0.4781111319681966</v>
       </c>
       <c r="C2" t="n">
-        <v>5.456553740203772</v>
+        <v>4.925428232206248</v>
       </c>
       <c r="D2" t="n">
-        <v>7.670394813280329</v>
+        <v>8.92310488389926</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.42754327743287</v>
+        <v>1.855503161026472</v>
       </c>
       <c r="C3" t="n">
-        <v>24.78422079371073</v>
+        <v>12.40438224315845</v>
       </c>
       <c r="D3" t="n">
-        <v>57.11808143307943</v>
+        <v>36.41793108903543</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.79644373451819</v>
+        <v>8.295768100885548</v>
       </c>
       <c r="C4" t="n">
-        <v>72.6709285637574</v>
+        <v>49.07265899677682</v>
       </c>
       <c r="D4" t="n">
-        <v>127.8569305148791</v>
+        <v>96.03946916794422</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.78090000216628</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C5" t="n">
-        <v>208.1059696077177</v>
+        <v>126.0073178400781</v>
       </c>
       <c r="D5" t="n">
-        <v>122.7430067234575</v>
+        <v>111.8701508989241</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.17494068446774</v>
+        <v>20.97111271041612</v>
       </c>
       <c r="C6" t="n">
-        <v>342.0988232741394</v>
+        <v>230.8834980939479</v>
       </c>
       <c r="D6" t="n">
-        <v>70.07813287684159</v>
+        <v>80.5838150599867</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.27108553955913</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>342.8508420155924</v>
+        <v>260.3270934920139</v>
       </c>
       <c r="D7" t="n">
-        <v>41.32176087174825</v>
+        <v>45.21439051908685</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.837250865273282</v>
       </c>
       <c r="C8" t="n">
-        <v>229.31662875797</v>
+        <v>151.1253328532327</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>75.32655610374501</v>
+        <v>58.68593251676156</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>23.51874800293658</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>28.61303684027329</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>18.12502611580461</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.745948328778329</v>
+        <v>0.3328124717396687</v>
       </c>
       <c r="C2" t="n">
-        <v>11.08884031946772</v>
+        <v>8.212319546024569</v>
       </c>
       <c r="D2" t="n">
-        <v>14.87740471015616</v>
+        <v>14.04291916154637</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.400234268163208</v>
+        <v>1.73278469799562</v>
       </c>
       <c r="C3" t="n">
-        <v>22.94344384824796</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D3" t="n">
-        <v>51.75773896789184</v>
+        <v>35.09748042682347</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.69961056469625</v>
+        <v>5.845325831085509</v>
       </c>
       <c r="C4" t="n">
-        <v>67.75728130400211</v>
+        <v>38.69656751059227</v>
       </c>
       <c r="D4" t="n">
-        <v>125.5085900063207</v>
+        <v>92.8615518492973</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.98921044191585</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C5" t="n">
-        <v>176.8618489200629</v>
+        <v>106.96141237769</v>
       </c>
       <c r="D5" t="n">
-        <v>135.5548142638784</v>
+        <v>121.0494919336317</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.90325861229863</v>
+        <v>23.90948358922682</v>
       </c>
       <c r="C6" t="n">
-        <v>338.9591941159581</v>
+        <v>216.2721470116427</v>
       </c>
       <c r="D6" t="n">
-        <v>85.53476873250337</v>
+        <v>95.47692773341082</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.20659329071511</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>406.270761962232</v>
+        <v>300.9302150442535</v>
       </c>
       <c r="D7" t="n">
-        <v>48.26860762699867</v>
+        <v>57.19171251089794</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>311.930698070339</v>
+        <v>250.5960102475196</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.38218726105504</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>147.9906124335726</v>
+        <v>122.6968645813578</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>50.25075624187299</v>
+        <v>48.68486865359933</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.310273332270997</v>
+        <v>4.214642894331557</v>
       </c>
       <c r="C2" t="n">
-        <v>10.3584200275081</v>
+        <v>6.622870012848982</v>
       </c>
       <c r="D2" t="n">
-        <v>12.7411217057151</v>
+        <v>5.695118432335748</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.00669230748048</v>
+        <v>0.6508987279156352</v>
       </c>
       <c r="C2" t="n">
-        <v>6.476589604916207</v>
+        <v>18.64927938987241</v>
       </c>
       <c r="D2" t="n">
-        <v>11.06822361767854</v>
+        <v>17.57033866290516</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.40929098167968</v>
+        <v>1.413716694115407</v>
       </c>
       <c r="C3" t="n">
-        <v>32.01479263548849</v>
+        <v>24.28843820306609</v>
       </c>
       <c r="D3" t="n">
-        <v>57.55986789999049</v>
+        <v>37.51257977927062</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.17780381212246</v>
+        <v>4.594579255875073</v>
       </c>
       <c r="C4" t="n">
-        <v>100.2128786586974</v>
+        <v>39.39851711912875</v>
       </c>
       <c r="D4" t="n">
-        <v>127.7548287536374</v>
+        <v>88.87958316087224</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.3668391506856</v>
+        <v>13.10633185169492</v>
       </c>
       <c r="C5" t="n">
-        <v>278.1291246131214</v>
+        <v>89.41267216427826</v>
       </c>
       <c r="D5" t="n">
-        <v>123.6511233498858</v>
+        <v>126.7436286182632</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.50947030524187</v>
+        <v>23.62772199810799</v>
       </c>
       <c r="C6" t="n">
-        <v>327.3667172242118</v>
+        <v>195.7035508599677</v>
       </c>
       <c r="D6" t="n">
-        <v>68.70957657712154</v>
+        <v>110.0077755039679</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="C7" t="n">
-        <v>219.36465228002</v>
+        <v>307.0386492600772</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>68.51028179315941</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C8" t="n">
-        <v>109.0672612032994</v>
+        <v>323.1962529765712</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>41.47393176590651</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>3.771874679716245</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>209.2281072336717</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>90.67912670275665</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>38.91549724863931</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.135923151542564</v>
+        <v>5.69119144151876</v>
       </c>
       <c r="C2" t="n">
-        <v>5.062872910800801</v>
+        <v>5.898340207114837</v>
       </c>
       <c r="D2" t="n">
-        <v>12.80002656796991</v>
+        <v>15.33195389722244</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.28518986031709</v>
+        <v>6.965499961631121</v>
       </c>
       <c r="C3" t="n">
-        <v>26.09976271740146</v>
+        <v>13.07687942056751</v>
       </c>
       <c r="D3" t="n">
-        <v>13.83773389135879</v>
+        <v>6.950773746067418</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39712574109244</v>
+        <v>11.67879149844286</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13789358571923</v>
+        <v>59.95112969200668</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576132440128522</v>
+        <v>0.7785860998961907</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.224861282001525</v>
+        <v>3.314380249537232</v>
       </c>
       <c r="C2" t="n">
-        <v>9.997136872345271</v>
+        <v>6.494261063592651</v>
       </c>
       <c r="D2" t="n">
-        <v>17.03528616409065</v>
+        <v>13.31053537417826</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.22476347101029</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="C3" t="n">
-        <v>22.12368451520187</v>
+        <v>19.72822011683965</v>
       </c>
       <c r="D3" t="n">
-        <v>21.24502031990098</v>
+        <v>18.69247628885927</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.18388992033042</v>
+        <v>8.70417514585222</v>
       </c>
       <c r="C4" t="n">
-        <v>40.31743297030376</v>
+        <v>21.81148874525138</v>
       </c>
       <c r="D4" t="n">
-        <v>22.32199755145973</v>
+        <v>17.8039946165159</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43895121958327</v>
+        <v>13.63181160432767</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13309627767511</v>
+        <v>73.77215691753797</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250305519912268</v>
+        <v>1.603742541685608</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.140831890063798</v>
+        <v>2.923644663247001</v>
       </c>
       <c r="C2" t="n">
-        <v>11.14479993860979</v>
+        <v>5.809982913732624</v>
       </c>
       <c r="D2" t="n">
-        <v>18.56190384419444</v>
+        <v>18.47551004622073</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.72054606165493</v>
+        <v>13.03270077387641</v>
       </c>
       <c r="C3" t="n">
-        <v>32.29949946972006</v>
+        <v>23.37050409959532</v>
       </c>
       <c r="D3" t="n">
-        <v>29.94330497952772</v>
+        <v>25.35363446217388</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.64481261970768</v>
+        <v>20.930861054542</v>
       </c>
       <c r="C4" t="n">
-        <v>49.21304891848411</v>
+        <v>39.1815508764902</v>
       </c>
       <c r="D4" t="n">
-        <v>27.95035713990669</v>
+        <v>23.29196428325558</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.68279768053704</v>
+        <v>8.39394287131023</v>
       </c>
       <c r="C5" t="n">
-        <v>44.76769531365456</v>
+        <v>26.53173170727006</v>
       </c>
       <c r="D5" t="n">
-        <v>30.67961575771283</v>
+        <v>26.48264432205772</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72976640419939</v>
+        <v>14.84672857346586</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0515750656163</v>
+        <v>87.4307349326323</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182441601049848</v>
+        <v>2.47445476224431</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.449681506274044</v>
+        <v>2.850013585428491</v>
       </c>
       <c r="C2" t="n">
-        <v>11.8182788637231</v>
+        <v>10.16697922517997</v>
       </c>
       <c r="D2" t="n">
-        <v>17.49278059426967</v>
+        <v>23.50696703048563</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.44842202112931</v>
+        <v>11.39809084630547</v>
       </c>
       <c r="C3" t="n">
-        <v>38.60722846950582</v>
+        <v>22.91399141712056</v>
       </c>
       <c r="D3" t="n">
-        <v>37.38986131623977</v>
+        <v>34.24826866264998</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.5967480399286</v>
+        <v>23.70037132822225</v>
       </c>
       <c r="C4" t="n">
-        <v>66.87665361329272</v>
+        <v>50.79562621772997</v>
       </c>
       <c r="D4" t="n">
-        <v>36.1950743601714</v>
+        <v>30.54118933141402</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.32279937271473</v>
+        <v>20.56761440397068</v>
       </c>
       <c r="C5" t="n">
-        <v>69.67954330891737</v>
+        <v>53.13709449235862</v>
       </c>
       <c r="D5" t="n">
-        <v>33.4285093296039</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.78744377426395</v>
+        <v>8.211337798320324</v>
       </c>
       <c r="C6" t="n">
-        <v>42.54600025894403</v>
+        <v>28.05540414426111</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04995237583614</v>
+        <v>16.09623870559298</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7544512137882</v>
+        <v>101.6604549826925</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01665079194538</v>
+        <v>3.388681832756416</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.440264939859076</v>
+        <v>2.240348261091221</v>
       </c>
       <c r="C2" t="n">
-        <v>11.20272305316035</v>
+        <v>5.660757262687108</v>
       </c>
       <c r="D2" t="n">
-        <v>25.98686173141307</v>
+        <v>19.00172681569702</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.04804888424586</v>
+        <v>10.51942665100457</v>
       </c>
       <c r="C3" t="n">
-        <v>40.0602150717911</v>
+        <v>32.63820242768521</v>
       </c>
       <c r="D3" t="n">
-        <v>39.85895679242051</v>
+        <v>44.49280595646545</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.49165997784518</v>
+        <v>23.01118443984099</v>
       </c>
       <c r="C4" t="n">
-        <v>69.04631603967817</v>
+        <v>54.53510322320607</v>
       </c>
       <c r="D4" t="n">
-        <v>40.30467025014855</v>
+        <v>39.98560224626834</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.91122610045706</v>
+        <v>28.49522711576368</v>
       </c>
       <c r="C5" t="n">
-        <v>73.21383504420589</v>
+        <v>75.54548584179207</v>
       </c>
       <c r="D5" t="n">
-        <v>31.04777114680538</v>
+        <v>33.67394625566561</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.91449013873929</v>
+        <v>18.03274183160542</v>
       </c>
       <c r="C6" t="n">
-        <v>52.5284109157256</v>
+        <v>57.51961624411638</v>
       </c>
       <c r="D6" t="n">
-        <v>31.35603992593888</v>
+        <v>35.70321876034376</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>26.23033516206628</v>
+        <v>29.8235317596096</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051343316756977</v>
+        <v>17.37319560989332</v>
       </c>
       <c r="C21" t="n">
-        <v>66.10634359459667</v>
+        <v>115.5317508057906</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407089572973111</v>
+        <v>4.34329890247333</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.806636759992384</v>
+        <v>2.956042337487146</v>
       </c>
       <c r="C2" t="n">
-        <v>5.112942043717388</v>
+        <v>8.019896995992195</v>
       </c>
       <c r="D2" t="n">
-        <v>20.45765866109504</v>
+        <v>19.4228965808189</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.36635612460008</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="C3" t="n">
-        <v>42.39186586937728</v>
+        <v>26.6397239547372</v>
       </c>
       <c r="D3" t="n">
-        <v>52.05717201768712</v>
+        <v>48.70450360768427</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.06896868567131</v>
+        <v>21.65833610338889</v>
       </c>
       <c r="C4" t="n">
-        <v>88.49670155621598</v>
+        <v>69.11012964045422</v>
       </c>
       <c r="D4" t="n">
-        <v>51.84216927045707</v>
+        <v>51.45928766580082</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.09056713516474</v>
+        <v>31.46501392111028</v>
       </c>
       <c r="C5" t="n">
-        <v>105.9796646734432</v>
+        <v>87.86641953008954</v>
       </c>
       <c r="D5" t="n">
-        <v>38.7054032399305</v>
+        <v>40.10439371848221</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.01136436629024</v>
+        <v>28.09565580013523</v>
       </c>
       <c r="C6" t="n">
-        <v>88.9561594818035</v>
+        <v>89.39892769641881</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.42027013287564</v>
+        <v>14.55244622005047</v>
       </c>
       <c r="C7" t="n">
-        <v>55.21545438224911</v>
+        <v>56.53295980134833</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>38.86640986342697</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>28.20561154301086</v>
+        <v>32.62838495064274</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.268624319560762</v>
+        <v>18.67294838376634</v>
       </c>
       <c r="C21" t="n">
-        <v>75.41197731544291</v>
+        <v>128.9322626498152</v>
       </c>
       <c r="D21" t="n">
-        <v>5.451468239670572</v>
+        <v>5.335128109647524</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.981968688425063</v>
+        <v>2.638937829015426</v>
       </c>
       <c r="C2" t="n">
-        <v>8.798422925459915</v>
+        <v>4.87535909928966</v>
       </c>
       <c r="D2" t="n">
-        <v>18.34788284466864</v>
+        <v>15.16505678750048</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.25068982194821</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="C3" t="n">
-        <v>29.15299807760903</v>
+        <v>41.94517066394497</v>
       </c>
       <c r="D3" t="n">
-        <v>56.02343274284423</v>
+        <v>54.1286596736479</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.48036203147973</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="C4" t="n">
-        <v>97.68586006796613</v>
+        <v>87.64159930581701</v>
       </c>
       <c r="D4" t="n">
-        <v>64.98777103032187</v>
+        <v>48.88121819444869</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.94454876913922</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="C5" t="n">
-        <v>138.2791641431633</v>
+        <v>53.4070751110265</v>
       </c>
       <c r="D5" t="n">
-        <v>48.64559874542947</v>
+        <v>34.65569395991241</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.55729820530948</v>
+        <v>9.016370915802709</v>
       </c>
       <c r="C6" t="n">
-        <v>131.9449279553629</v>
+        <v>37.23278168356029</v>
       </c>
       <c r="D6" t="n">
-        <v>38.80259626265094</v>
+        <v>25.60005313593983</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>94.44118390543041</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>27.60772719112455</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>51.7381040138069</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>29.95312245657017</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.471330400707015</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.05246700795392</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.537414100618639</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
